--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N52_analysis.xlsx
@@ -481,11 +481,11 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.5759569032954029</v>
+        <v>0.09359299678550298</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -509,11 +509,11 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>3.885710053143092</v>
+        <v>0.6314278836357525</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -537,11 +537,11 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>8.95267718612541</v>
+        <v>1.454810042745379</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -565,11 +565,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>12.72822867982764</v>
+        <v>2.068337160471991</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -593,11 +593,11 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6501752920692249</v>
+        <v>0.105653484961249</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>4.323117209101329</v>
+        <v>0.702506546478966</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -649,11 +649,11 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>4.537742953397743</v>
+        <v>0.7373832299271332</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>4.015779367308909</v>
+        <v>0.6525641471876977</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -705,11 +705,11 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1.320730519141089</v>
+        <v>0.214618709360427</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -733,11 +733,11 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>12.22798616070418</v>
+        <v>1.987047751114429</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -761,11 +761,11 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>1.396137617513335</v>
+        <v>0.226872362845917</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -789,11 +789,11 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>6.491082390239559</v>
+        <v>1.054800888413928</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -817,11 +817,11 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>7.299506596703245</v>
+        <v>1.186169821964277</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -845,11 +845,11 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.8889371128894032</v>
+        <v>0.144452280844528</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -873,11 +873,11 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>8.276472678623424</v>
+        <v>1.344926810276307</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -901,11 +901,11 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>9.7072785444498</v>
+        <v>1.577432763473092</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -929,11 +929,11 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>9.192388155425117</v>
+        <v>1.493763075256582</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>2.582244895938807</v>
+        <v>0.4196147955900562</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -985,11 +985,11 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>1.622099225893446</v>
+        <v>0.2635911242076849</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1013,11 +1013,11 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>4.447342463022216</v>
+        <v>0.7226931502411101</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>6.644621633834139</v>
+        <v>1.079751015498048</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1069,11 +1069,11 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>1.425647468038645</v>
+        <v>0.2316677135562799</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1097,11 +1097,11 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>3.640054944640259</v>
+        <v>0.5915089285040421</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1125,11 +1125,11 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>7.049216596298085</v>
+        <v>1.145497696898439</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1153,11 +1153,11 @@
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>5.789780502120659</v>
+        <v>0.9408393315946072</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1181,11 +1181,11 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>4.74217072277324</v>
+        <v>0.7706027424506515</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1209,11 +1209,11 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>2.931600737461549</v>
+        <v>0.4763851198375017</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1237,11 +1237,11 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>6.403124237432849</v>
+        <v>1.040507688582838</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1265,11 +1265,11 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>5.893416124014914</v>
+        <v>0.9576801201524235</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1293,11 +1293,11 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>7.588968320977648</v>
+        <v>1.233207352158868</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1321,11 +1321,11 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>3.185832760279013</v>
+        <v>0.5176978235453396</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1349,11 +1349,11 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>7.94390829581673</v>
+        <v>1.290885098070219</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1377,11 +1377,11 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>2.949059344785446</v>
+        <v>0.4792221435276349</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1405,11 +1405,11 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>10.49283645437388</v>
+        <v>1.705085923835756</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1433,11 +1433,11 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>6.453349211801325</v>
+        <v>1.048669246917715</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1461,11 +1461,11 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>3.155981539670029</v>
+        <v>0.5128470001963797</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1489,11 +1489,11 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>11.75863787123243</v>
+        <v>1.91077865407527</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1517,11 +1517,11 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>8.658676314204502</v>
+        <v>1.407034901058232</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>5.571339539378164</v>
+        <v>0.9053426751489517</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1573,11 +1573,11 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>4.664952173987245</v>
+        <v>0.7580547282729273</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1601,11 +1601,11 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>5.231777797531677</v>
+        <v>0.8501638920988975</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1629,11 +1629,11 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>6.778947617586432</v>
+        <v>1.101578987857795</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1657,11 +1657,11 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>3.964292183395113</v>
+        <v>0.6441974798017059</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1685,11 +1685,11 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>6.884521849163344</v>
+        <v>1.118734800489044</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1713,11 +1713,11 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>6.388049553982378</v>
+        <v>1.038058052522136</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1741,11 +1741,11 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>3.333403432067864</v>
+        <v>0.5416780577110279</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1769,11 +1769,11 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>5.416595441127159</v>
+        <v>0.8801967591831633</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1797,11 +1797,11 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>2.549661076484142</v>
+        <v>0.414319924928673</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1825,11 +1825,11 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>8.713578330369918</v>
+        <v>1.415956478685112</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1853,11 +1853,11 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>7.324000683398571</v>
+        <v>1.190150111052268</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1881,11 +1881,11 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>6.128258770283415</v>
+        <v>0.9958420501710551</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>5.38779244218839</v>
+        <v>0.8755162718556134</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1937,11 +1937,11 @@
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>2.166282502741991</v>
+        <v>0.3520209066955735</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -1965,11 +1965,11 @@
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>1.720227796970329</v>
+        <v>0.2795370170076785</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -1993,11 +1993,11 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>6.771510034104495</v>
+        <v>1.10037038054198</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2021,11 +2021,11 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>6.486526461776778</v>
+        <v>1.054060550038727</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2049,11 +2049,11 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>2.127635512706472</v>
+        <v>0.3457407708148018</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2077,11 +2077,11 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>4.743416490252569</v>
+        <v>0.7708051796660425</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2105,11 +2105,11 @@
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>0.65</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>7.915872789590237</v>
+        <v>1.286329328308414</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2161,11 +2161,11 @@
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>2.549509756796392</v>
+        <v>0.4142953354794138</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2189,11 +2189,11 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>4.606311359302903</v>
+        <v>0.7485255958867217</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2217,11 +2217,11 @@
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>2.23606797749979</v>
+        <v>0.3633610463437159</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2245,11 +2245,11 @@
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>11.84675816467719</v>
+        <v>1.925098201760044</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2273,11 +2273,11 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>3.518768202443223</v>
+        <v>0.5717998328970237</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2301,11 +2301,11 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>7.755682902488379</v>
+        <v>1.260298471654362</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2329,11 +2329,11 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>1.845972582084995</v>
+        <v>0.2999705445888117</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2357,11 +2357,11 @@
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>4.117797734783805</v>
+        <v>0.6691421319023683</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2385,11 +2385,11 @@
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>2.976881040815227</v>
+        <v>0.4837431691324744</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2413,11 +2413,11 @@
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>1.736583434230975</v>
+        <v>0.2821948080625334</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2441,11 +2441,11 @@
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>8.056853372070266</v>
+        <v>1.309238672961418</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2469,11 +2469,11 @@
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>0.7071067811865476</v>
+        <v>0.114904851942814</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2497,11 +2497,11 @@
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
-        <v>13.61893479130693</v>
+        <v>2.213076903587377</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2525,11 +2525,11 @@
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>6.086257106627546</v>
+        <v>0.9890167798269762</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>4.743416490252569</v>
+        <v>0.7708051796660425</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2581,11 +2581,11 @@
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>9.692057006417325</v>
+        <v>1.574959263542815</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2609,11 +2609,11 @@
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>1.912048933068653</v>
+        <v>0.3107079516236562</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2637,11 +2637,11 @@
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>2.549509756796392</v>
+        <v>0.4142953354794138</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2665,11 +2665,11 @@
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>2.967966555121758</v>
+        <v>0.4822945652072858</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2693,11 +2693,11 @@
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>6.387681045246582</v>
+        <v>1.03799816985257</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2721,11 +2721,11 @@
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>4.442927926396532</v>
+        <v>0.7219757880394365</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2749,11 +2749,11 @@
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>4.464078567448523</v>
+        <v>0.7254127672103851</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2777,11 +2777,11 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>7.145187961757146</v>
+        <v>1.161093043785536</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2805,11 +2805,11 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>12.77348648332313</v>
+        <v>2.075691553540008</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>3.106404204234112</v>
+        <v>0.5047906831880432</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
